--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N54" headerRowCount="1">
-  <autoFilter ref="A10:N54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N55" headerRowCount="1">
+  <autoFilter ref="A10:N55"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3035</v>
+        <v>4096</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2104</v>
+        <v>2803</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>859</v>
+        <v>1277</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>381</v>
+        <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>314</v>
+        <v>430</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>250</v>
+        <v>392</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,50 +1018,50 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>01676</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>DESENZANO DEL GARDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>137</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>108</v>
+        <v>293</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,50 +1072,50 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01676</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DESENZANO DEL GARDA</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>6</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>25</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1685,35 +1685,35 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
@@ -1751,35 +1751,35 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,39 +1843,39 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,104 +1936,104 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,105 +2113,105 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,20 +2221,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>13</v>
@@ -2243,13 +2243,13 @@
         <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,86 +2275,86 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K38" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,47 +2441,47 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L41" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2495,47 +2495,47 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,35 +2545,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2603,28 +2603,28 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>2</v>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="K46" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,105 +2815,105 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01523</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CISANO BERGAMASCO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,89 +2923,89 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>01523</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CISANO BERGAMASCO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3038,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
@@ -3170,6 +3170,56 @@
         <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>01658</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>GRAZIOSI DAVIDE</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1182170542635659</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>219</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.0228310502283105</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>256</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.1796875</v>
+        <v>46</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>294</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1530612244897959</v>
+        <v>45</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>293</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.05460750853242321</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>150</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.5933333333333334</v>
+        <v>89</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>59</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1864406779661017</v>
+        <v>11</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>134</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.03731343283582089</v>
+        <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>200</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.235</v>
+        <v>47</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>173</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.03468208092485549</v>
+        <v>6</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>167</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.3652694610778443</v>
+        <v>61</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>67</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.1791044776119403</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>179</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.08379888268156424</v>
+        <v>15</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>90</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1222222222222222</v>
+        <v>11</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>83</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.4096385542168675</v>
+        <v>34</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>142</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.2253521126760563</v>
+        <v>32</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>96</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.07291666666666667</v>
+        <v>7</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>91</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>7</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>40</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.8</v>
+        <v>32</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>56</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.75</v>
+        <v>42</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>42</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>57</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.05263157894736842</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>38</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.1578947368421053</v>
+        <v>6</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>40</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.075</v>
+        <v>3</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.02222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>24</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.04166666666666666</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>24</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.2083333333333333</v>
+        <v>5</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>28</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.8571428571428571</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>43</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.06976744186046512</v>
+        <v>3</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>36</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.05555555555555555</v>
+        <v>2</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>13</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>25</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>10</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4096</v>
+        <v>4329</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2803</v>
+        <v>2952</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1277</v>
+        <v>1375</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>25</v>
@@ -1211,23 +1211,23 @@
         <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>94</v>
-      </c>
       <c r="L18" s="12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>26</v>
@@ -1265,19 +1265,19 @@
         <v>26</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -1319,16 +1319,16 @@
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>6</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>90</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,39 +1573,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K25" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L25" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>2</v>
@@ -1697,19 +1697,19 @@
         <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,35 +1739,35 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>7</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>3</v>
@@ -1913,7 +1913,7 @@
         <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>14</v>
@@ -1922,10 +1922,10 @@
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1955,35 +1955,35 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="G32" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2009,19 +2009,19 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>10</v>
@@ -2030,14 +2030,14 @@
         <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>4</v>
@@ -2084,10 +2084,10 @@
         <v>9</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,39 +2167,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>2</v>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>3</v>
@@ -2246,7 +2246,7 @@
         <v>19</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
@@ -2300,7 +2300,7 @@
         <v>13</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>1</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>2</v>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -2387,101 +2387,101 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PIANTEDO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K41" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,105 +2599,105 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="I44" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J44" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>PIANTEDO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L46" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         <v>10</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>8</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2984,13 +2984,13 @@
         <v>9</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>6</v>
@@ -3002,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4329</v>
+        <v>4613</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2952</v>
+        <v>3132</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1375</v>
+        <v>1485</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>622</v>
+        <v>678</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>95</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>18</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>5</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>26</v>
@@ -1265,23 +1265,23 @@
         <v>26</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -1319,19 +1319,19 @@
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>139</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>44</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,35 +1577,35 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,35 +1739,35 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>3</v>
@@ -1805,16 +1805,16 @@
         <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>73</v>
@@ -1859,7 +1859,7 @@
         <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>23</v>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>61</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="G32" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>66</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>11</v>
@@ -1976,14 +1976,14 @@
         <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>72</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>3</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>58</v>
@@ -2081,13 +2081,13 @@
         <v>4</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,212 +2098,212 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J37" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="M38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,25 +2387,25 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>18</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
@@ -2456,13 +2456,13 @@
         <v>19</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>3</v>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,39 +2599,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
         <v>22</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>2</v>
@@ -2669,7 +2669,7 @@
         <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>6</v>
@@ -2678,10 +2678,10 @@
         <v>3</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>37</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>15</v>
@@ -2732,10 +2732,10 @@
         <v>3</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2765,16 +2765,16 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>9</v>
@@ -2783,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>2</v>
@@ -2822,7 +2822,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
@@ -2876,13 +2876,13 @@
         <v>11</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>8</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>2</v>
@@ -2984,13 +2984,13 @@
         <v>9</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>6</v>
@@ -3002,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -3038,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4613</v>
+        <v>4860</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3132</v>
+        <v>3303</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1485</v>
+        <v>1590</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
         <v>288</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>37</v>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>25</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01640</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>SERIATE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>147</v>
+        <v>226</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01640</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SERIATE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -1319,19 +1319,19 @@
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>31</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>8</v>
+        <v>268</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>258</v>
+        <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1688,13 +1688,13 @@
         <v>108</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>77</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>16</v>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>8</v>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
@@ -1859,16 +1859,16 @@
         <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
@@ -1901,19 +1901,19 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>16</v>
@@ -1922,14 +1922,14 @@
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="G32" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>5</v>
@@ -2021,23 +2021,23 @@
         <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>39</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>8</v>
@@ -2120,7 +2120,7 @@
         <v>37</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>2</v>
@@ -2138,122 +2138,122 @@
         <v>8</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>56</v>
@@ -2297,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2314,66 +2314,66 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,56 +2383,56 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2441,47 +2441,47 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L42" s="12" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,66 +2530,66 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>PIANTEDO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>24</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2603,31 +2603,31 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,66 +2638,66 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PIANTEDO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2711,35 +2711,35 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>38</v>
@@ -2774,10 +2774,10 @@
         <v>25</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>1</v>
@@ -2786,10 +2786,10 @@
         <v>10</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
@@ -2882,7 +2882,7 @@
         <v>30</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>8</v>
@@ -2908,108 +2908,108 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01523</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>CISANO BERGAMASCO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="12" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>01523</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CISANO BERGAMASCO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
         <v>9</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L51" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3196,13 +3196,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4860</v>
+        <v>5143</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3303</v>
+        <v>3491</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1590</v>
+        <v>1690</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>715</v>
+        <v>758</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>37</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>28</v>
@@ -1274,14 +1274,14 @@
         <v>101</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -1319,16 +1319,16 @@
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>9</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>16</v>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>30</v>
@@ -1544,7 +1544,7 @@
         <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>38</v>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>38</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>3</v>
@@ -1643,16 +1643,16 @@
         <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>15</v>
@@ -1688,13 +1688,13 @@
         <v>108</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>77</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
@@ -1751,23 +1751,23 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>35</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
@@ -1859,16 +1859,16 @@
         <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>52</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>85</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>37</v>
@@ -1976,14 +1976,14 @@
         <v>16</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>5</v>
@@ -2021,7 +2021,7 @@
         <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>11</v>
@@ -2030,7 +2030,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>4</v>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>4</v>
@@ -2084,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>8</v>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2171,31 +2171,31 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,32 +2275,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2333,47 +2333,47 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>2</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,23 +2507,23 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>7</v>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,155 +2692,155 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K46" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>01523</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>CISANO BERGAMASCO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,93 +2869,93 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01523</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CISANO BERGAMASCO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
         <v>11</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>82</v>
-      </c>
       <c r="I50" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -3024,11 +3024,7 @@
           <t>CASAZZA</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
@@ -3078,11 +3074,7 @@
           <t>PIANICO</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
@@ -3132,11 +3124,7 @@
           <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>CARMINATI SIMONE</t>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N55" headerRowCount="1">
-  <autoFilter ref="A10:N55"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O55" headerRowCount="1">
+  <autoFilter ref="A10:O55"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA DALMAZIA 44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>758</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>550</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>281</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>641</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S S 11 KM 224 + 521</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>453</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>543</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PALAZZOLO S.S.469</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>304</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>315</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BROSETA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>516</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA MARCONI</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA MONTELUNGO, 10  - TANG. OVEST PALAZZOLI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>285</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>341</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PICCINELLI 78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA STELLA ALPINA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>245</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>30</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>MANTOVA SS 10</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PIACENZA, 50</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>88</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA FRANCESCO VAINI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>52</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>CA' BIANCA SS 39</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>38</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>28</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M40" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>SS 42 KM 117+560</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE 1146</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="N46" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS342 KM 18+640</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>46</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>46</v>
       </c>
       <c r="H48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2864,42 +3070,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S S 42</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M49" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2918,42 +3129,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE BORNATA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2972,20 +3188,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G51" s="12" t="n">
         <v>0</v>
       </c>
@@ -2993,21 +3211,24 @@
         <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3024,27 +3245,29 @@
           <t>CASAZZA</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>VIA NAZIONALE 25</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
       </c>
@@ -3057,7 +3280,10 @@
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3074,21 +3300,23 @@
           <t>PIANICO</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>SS 42 KM 57.700</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +3335,10 @@
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="N53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3124,21 +3355,23 @@
           <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>VIA ROMANA ZAITA 68</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
@@ -3157,7 +3390,10 @@
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3174,27 +3410,29 @@
           <t>BRESCIA</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>VIA LAMARMORA  150</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J55" s="12" t="n">
         <v>0</v>
       </c>
@@ -3207,7 +3445,10 @@
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O55" headerRowCount="1">
-  <autoFilter ref="A10:O55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O56" headerRowCount="1">
+  <autoFilter ref="A10:O56"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5143</v>
+        <v>5396</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3491</v>
+        <v>3658</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1690</v>
+        <v>1809</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>27</v>
@@ -1090,23 +1090,23 @@
         <v>7</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>48</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>22</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>46</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>245</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>7</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
@@ -1385,16 +1385,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>9</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1553,13 +1553,13 @@
         <v>139</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>80</v>
@@ -1612,13 +1612,13 @@
         <v>125</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>99</v>
@@ -1630,10 +1630,10 @@
         <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>282</v>
+        <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 16+700</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I29" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="J29" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>25</v>
@@ -1984,10 +1984,10 @@
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,14 +2018,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>5</v>
@@ -2034,40 +2034,40 @@
         <v>7</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 55+370</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>37</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>8</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,52 +2317,52 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,94 +2490,94 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>SS 42 KM 117+560</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,55 +2588,55 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 117+560</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,13 +2671,13 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -2689,13 +2689,13 @@
         <v>6</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2730,25 +2730,25 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="K43" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>34</v>
@@ -2789,10 +2789,10 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>0</v>
@@ -2801,16 +2801,16 @@
         <v>3</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>2</v>
@@ -2848,31 +2848,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>40</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>13</v>
@@ -2925,10 +2925,10 @@
         <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>3</v>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>7</v>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>15</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>9</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>13</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>1</v>
@@ -3146,13 +3146,13 @@
         <v>11</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>8</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>3</v>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01522</t>
+          <t>01691</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CASAZZA</t>
+          <t>CELLATICA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 25</t>
+          <t>ST PR BRESCIA BRIO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3285,24 +3285,24 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01639</t>
+          <t>01522</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PIANICO</t>
+          <t>CASAZZA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 57.700</t>
+          <t>VIA NAZIONALE 25</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -3315,13 +3315,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3347,30 +3347,30 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02053</t>
+          <t>01639</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BAGNOLO SAN VITO</t>
+          <t>PIANICO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMANA ZAITA 68</t>
+          <t>SS 42 KM 57.700</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -3395,60 +3395,115 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01658</t>
+          <t>02053</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA LAMARMORA  150</t>
+          <t>VIA ROMANA ZAITA 68</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>CARMINATI SIMONE</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>01658</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>VIA LAMARMORA  150</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="F55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="12" t="n">
+      <c r="F56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="J56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>46</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5396</v>
+        <v>5623</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3658</v>
+        <v>3821</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1809</v>
+        <v>1916</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>678</v>
+        <v>718</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>7</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>48</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE 84</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1553,13 +1553,13 @@
         <v>139</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>80</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>24</v>
@@ -1689,10 +1689,10 @@
         <v>67</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>197</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>67</v>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
@@ -1798,23 +1798,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1848,13 +1848,13 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>77</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>3</v>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>25</v>
@@ -1984,10 +1984,10 @@
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>61</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,14 +2077,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>5</v>
@@ -2093,19 +2093,19 @@
         <v>7</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
@@ -2202,13 +2202,13 @@
         <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>37</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,94 +2431,94 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>SS 42 KM 117+560</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,76 +2529,76 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 117+560</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,35 +2608,35 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
@@ -2683,23 +2683,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2742,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>8</v>
@@ -2751,7 +2751,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>7</v>
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>7</v>
@@ -2810,10 +2810,10 @@
         <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2848,52 +2848,52 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,39 +2962,39 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3025,19 +3025,19 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>13</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>1</v>
@@ -3152,7 +3152,7 @@
         <v>30</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>8</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>3</v>
@@ -3315,13 +3315,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O56" headerRowCount="1">
-  <autoFilter ref="A10:O56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O57" headerRowCount="1">
+  <autoFilter ref="A10:O57"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5623</v>
+        <v>5879</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3821</v>
+        <v>3984</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1916</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>832</v>
+        <v>877</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>582</v>
+        <v>616</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>27</v>
@@ -1090,23 +1090,23 @@
         <v>8</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>1</v>
@@ -1326,19 +1326,19 @@
         <v>7</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>234</v>
@@ -1444,16 +1444,16 @@
         <v>80</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>20</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1553,13 +1553,13 @@
         <v>139</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>80</v>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>125</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>12</v>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L27" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M27" s="12" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1848,13 +1848,13 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>77</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>3</v>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>1</v>
@@ -1975,19 +1975,19 @@
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
@@ -2034,19 +2034,19 @@
         <v>8</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>5</v>
@@ -2093,23 +2093,23 @@
         <v>7</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>8</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,32 +2313,32 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L36" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>0</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2494,25 +2494,25 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>38</v>
@@ -2553,22 +2553,22 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>7</v>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>34</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2751,10 +2751,10 @@
         <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,10 +2789,10 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>1</v>
@@ -2801,16 +2801,16 @@
         <v>3</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>3</v>
@@ -2848,22 +2848,22 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>0</v>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,39 +2962,39 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3025,19 +3025,19 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>S S 42</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>13</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K49" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N49" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L49" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIALE BORNATA</t>
+          <t>S S 42</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 236 KM 14+332</t>
+          <t>VIALE BORNATA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,39 +3198,39 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3292,36 +3292,36 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01522</t>
+          <t>01688</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CASAZZA</t>
+          <t>MANERBIO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 25</t>
+          <t>VIA BRESCIA 18</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3340,24 +3340,24 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01639</t>
+          <t>01522</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PIANICO</t>
+          <t>CASAZZA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 57.700</t>
+          <t>VIA NAZIONALE 25</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -3370,13 +3370,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>0</v>
@@ -3402,30 +3402,30 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02053</t>
+          <t>01639</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BAGNOLO SAN VITO</t>
+          <t>PIANICO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMANA ZAITA 68</t>
+          <t>SS 42 KM 57.700</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3450,62 +3450,117 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01658</t>
+          <t>02053</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA LAMARMORA  150</t>
+          <t>VIA ROMANA ZAITA 68</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>CARMINATI SIMONE</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>01658</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>VIA LAMARMORA  150</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="F56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="12" t="n">
+      <c r="F57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
+      <c r="J57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5879</v>
+        <v>6067</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3984</v>
+        <v>4113</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2024</v>
+        <v>2100</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>877</v>
+        <v>907</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>100</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>27</v>
@@ -1090,23 +1090,23 @@
         <v>8</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>91</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>22</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>221</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>1</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>218</v>
+      </c>
+      <c r="G20" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>201</v>
-      </c>
       <c r="H20" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>8</v>
@@ -1391,17 +1391,17 @@
         <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>72</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>8</v>
+        <v>333</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1848,13 +1848,13 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>77</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>3</v>
@@ -1925,10 +1925,10 @@
         <v>36</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO VAINI</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>VIA FRANCESCO VAINI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>5</v>
@@ -2093,16 +2093,16 @@
         <v>7</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>4</v>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>11</v>
@@ -2220,7 +2220,7 @@
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>8</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="J35" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="K35" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>69</v>
-      </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I37" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2435,35 +2435,35 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>48</v>
@@ -2506,7 +2506,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>8</v>
@@ -2515,7 +2515,7 @@
         <v>17</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>3</v>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>9</v>
@@ -2633,14 +2633,14 @@
         <v>14</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>3</v>
@@ -2683,16 +2683,16 @@
         <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>2</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2742,16 +2742,16 @@
         <v>10</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>8</v>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE DI VITTORIO 17</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,39 +2844,39 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K45" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L45" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>47</v>
@@ -2916,10 +2916,10 @@
         <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>5</v>
@@ -2966,31 +2966,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K47" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L47" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M47" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>18</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>12</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>1</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>1</v>
@@ -3205,13 +3205,13 @@
         <v>11</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6067</v>
+        <v>6308</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4113</v>
+        <v>4295</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2100</v>
+        <v>2210</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>907</v>
+        <v>950</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>797</v>
+        <v>848</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>633</v>
+        <v>673</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>368</v>
+        <v>230</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE 84</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>215</v>
+        <v>387</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>70</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="J24" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>80</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>182</v>
+        <v>15</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
         <v>125</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>12</v>
@@ -1848,13 +1848,13 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>77</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>3</v>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>72</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>1</v>
@@ -2043,10 +2043,10 @@
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>33</v>
@@ -2099,10 +2099,10 @@
         <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>4</v>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         <v>50</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>17</v>
@@ -2279,7 +2279,7 @@
         <v>33</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2320,49 +2320,49 @@
         <v>49</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>3</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>1</v>
@@ -2470,22 +2470,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01679</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>EDOLO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 117+560</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,87 +2494,87 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01679</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>EDOLO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>SS 42 KM 117+560</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="M40" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>3</v>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,39 +2608,39 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>3</v>
@@ -2683,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>4</v>
@@ -2692,14 +2692,14 @@
         <v>23</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2742,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>9</v>
@@ -2751,10 +2751,10 @@
         <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
@@ -2801,23 +2801,23 @@
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>1</v>
@@ -2860,7 +2860,7 @@
         <v>3</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>7</v>
@@ -2869,7 +2869,7 @@
         <v>10</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>3</v>
@@ -2910,13 +2910,13 @@
         <v>32</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>18</v>
@@ -2928,7 +2928,7 @@
         <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>5</v>
@@ -2972,7 +2972,7 @@
         <v>49</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>21</v>
@@ -2987,10 +2987,10 @@
         <v>7</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3025,19 +3025,19 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>1</v>
@@ -3105,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>3</v>
@@ -3146,7 +3146,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>1</v>
@@ -3205,13 +3205,13 @@
         <v>11</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6308</v>
+        <v>6599</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4295</v>
+        <v>4511</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2210</v>
+        <v>2331</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>23</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>221</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>90</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>25</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>139</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>80</v>
@@ -1748,7 +1748,7 @@
         <v>60</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1789,7 +1789,7 @@
         <v>125</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>12</v>
@@ -1848,7 +1848,7 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>24</v>
@@ -1984,10 +1984,10 @@
         <v>17</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>44</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G32" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>106</v>
-      </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 55+370</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>1</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
@@ -2506,23 +2506,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>3</v>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>19</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>3</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>3</v>
@@ -2683,16 +2683,16 @@
         <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>2</v>
@@ -2706,135 +2706,135 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PIANTEDO</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 1146</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>PIANTEDO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>VIA NAZIONALE 1146</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE DI VITTORIO 17</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K45" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,39 +2962,39 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3025,19 +3025,19 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>51</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>1</v>
@@ -3211,7 +3211,7 @@
         <v>30</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>8</v>
@@ -3535,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6599</v>
+        <v>6879</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4511</v>
+        <v>4721</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2331</v>
+        <v>2513</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>994</v>
+        <v>1036</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>896</v>
+        <v>941</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>697</v>
+        <v>730</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>697</v>
+        <v>726</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>221</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>90</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>29</v>
@@ -1689,10 +1689,10 @@
         <v>71</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1730,13 +1730,13 @@
         <v>139</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>80</v>
@@ -1789,13 +1789,13 @@
         <v>125</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>99</v>
@@ -1848,13 +1848,13 @@
         <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>77</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>22</v>
@@ -2109,125 +2109,125 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>02766</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>SONDRIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>CA' BIANCA SS 39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02766</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SONDRIO</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CA' BIANCA SS 39</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2258,52 +2258,52 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="J38" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M38" s="12" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>50</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>29</v>
@@ -2574,7 +2574,7 @@
         <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>3</v>
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>26</v>
@@ -2630,13 +2630,13 @@
         <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>5</v>
@@ -2692,7 +2692,7 @@
         <v>23</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>2</v>
@@ -2706,118 +2706,118 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>PIANTEDO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>VIA NAZIONALE 1146</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PIANTEDO</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 1146</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
         <v>40</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2848,31 +2848,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>1</v>
@@ -2969,13 +2969,13 @@
         <v>33</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>19</v>
@@ -2987,7 +2987,7 @@
         <v>14</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>6</v>
@@ -3028,7 +3028,7 @@
         <v>20</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>51</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>1</v>
@@ -3105,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>3</v>
@@ -3146,7 +3146,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>1</v>
@@ -3205,13 +3205,13 @@
         <v>11</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FEDERICI MAURO.xlsx
@@ -684,13 +684,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6879</v>
+        <v>6873</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2513</v>
+        <v>2487</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>121</v>
@@ -854,7 +854,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>220</v>
@@ -863,7 +863,7 @@
         <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>118</v>
@@ -904,16 +904,16 @@
         <v>566</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>152</v>
@@ -922,14 +922,14 @@
         <v>171</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>114</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>121</v>
@@ -981,7 +981,7 @@
         <v>195</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>138</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>70</v>
@@ -1031,7 +1031,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>135</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>61</v>
@@ -1099,14 +1099,14 @@
         <v>160</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         <v>375</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>109</v>
@@ -1149,7 +1149,7 @@
         <v>77</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>104</v>
@@ -1158,10 +1158,10 @@
         <v>60</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>159</v>
@@ -1208,7 +1208,7 @@
         <v>88</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>103</v>
@@ -1217,10 +1217,10 @@
         <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>42</v>
@@ -1267,7 +1267,7 @@
         <v>42</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>47</v>
@@ -1276,14 +1276,14 @@
         <v>120</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>89</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>52</v>
@@ -1326,7 +1326,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>33</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
@@ -1385,7 +1385,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>23</v>
@@ -1435,16 +1435,16 @@
         <v>204</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>57</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>46</v>
@@ -1512,7 +1512,7 @@
         <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>139</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>1</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>44</v>
@@ -1571,7 +1571,7 @@
         <v>32</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>16</v>
@@ -1621,7 +1621,7 @@
         <v>379</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>51</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>12</v>
@@ -1680,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>29</v>
@@ -1689,7 +1689,7 @@
         <v>71</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>39</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>20</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>12</v>
@@ -1798,7 +1798,7 @@
         <v>52</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>30</v>
@@ -1807,7 +1807,7 @@
         <v>23</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>39</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>2</v>
@@ -1857,7 +1857,7 @@
         <v>54</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>29</v>
@@ -1907,7 +1907,7 @@
         <v>104</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>30</v>
@@ -1916,7 +1916,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
@@ -1925,7 +1925,7 @@
         <v>38</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>102</v>
@@ -1975,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>29</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>73</v>
@@ -2093,7 +2093,7 @@
         <v>101</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>20</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>24</v>
@@ -2152,7 +2152,7 @@
         <v>15</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>17</v>
@@ -2161,14 +2161,14 @@
         <v>11</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>14</v>
@@ -2220,7 +2220,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>5</v>
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>16</v>
@@ -2279,14 +2279,14 @@
         <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2320,16 +2320,16 @@
         <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>1</v>
@@ -2338,14 +2338,14 @@
         <v>39</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>15</v>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>2</v>
@@ -2565,7 +2565,7 @@
         <v>26</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>9</v>
@@ -2581,24 +2581,24 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
         <v>46</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,39 +2667,39 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>9</v>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>12</v>
@@ -2851,16 +2851,16 @@
         <v>39</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>59</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>11</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>1</v>
@@ -2919,7 +2919,7 @@
         <v>3</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>7</v>
@@ -2928,7 +2928,7 @@
         <v>10</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>3</v>
@@ -2972,13 +2972,13 @@
         <v>56</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>1</v>
@@ -3028,16 +3028,16 @@
         <v>20</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>5</v>
@@ -3105,14 +3105,14 @@
         <v>1</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>1</v>
@@ -3155,7 +3155,7 @@
         <v>4</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>3</v>
@@ -3164,7 +3164,7 @@
         <v>3</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
@@ -3202,19 +3202,19 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>1</v>
@@ -3230,24 +3230,24 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01691</t>
+          <t>01522</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CELLATICA</t>
+          <t>CASAZZA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ST PR BRESCIA BRIO</t>
+          <t>VIA NAZIONALE 25</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3285,37 +3285,37 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01688</t>
+          <t>01639</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MANERBIO</t>
+          <t>PIANICO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA BRESCIA 18</t>
+          <t>SS 42 KM 57.700</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
@@ -3340,43 +3340,43 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01522</t>
+          <t>02053</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CASAZZA</t>
+          <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 25</t>
+          <t>VIA ROMANA ZAITA 68</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>0</v>
@@ -3402,36 +3402,36 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01639</t>
+          <t>01658</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PIANICO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 42 KM 57.700</t>
+          <t>VIA LAMARMORA  150</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>0</v>
@@ -3457,30 +3457,30 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02053</t>
+          <t>01691</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BAGNOLO SAN VITO</t>
+          <t>CELLATICA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMANA ZAITA 68</t>
+          <t>ST PR BRESCIA BRIO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>0</v>
@@ -3512,36 +3512,36 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01658</t>
+          <t>01688</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>MANERBIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA LAMARMORA  150</t>
+          <t>VIA BRESCIA 18</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>
